--- a/xiuxian配置表/yunxing_params/z_shijian_rules.xlsx
+++ b/xiuxian配置表/yunxing_params/z_shijian_rules.xlsx
@@ -538,7 +538,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>major_realm_multipliers:qi</t>
+          <t>major_realm_multipliers:lianqi</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -553,7 +553,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>major_realm_multipliers:foundation</t>
+          <t>major_realm_multipliers:zhuji</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -568,7 +568,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>major_realm_multipliers:core</t>
+          <t>major_realm_multipliers:jindan</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -583,7 +583,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>major_realm_multipliers:nascent</t>
+          <t>major_realm_multipliers:yuanying</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -598,7 +598,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>major_realm_multipliers:transform</t>
+          <t>major_realm_multipliers:huashen</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -613,7 +613,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>major_realm_multipliers:void</t>
+          <t>major_realm_multipliers:lianxu</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -628,7 +628,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>major_realm_multipliers:merge</t>
+          <t>major_realm_multipliers:heti</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -643,7 +643,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>major_realm_multipliers:great</t>
+          <t>major_realm_multipliers:dacheng</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -658,7 +658,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>major_realm_multipliers:tribulation</t>
+          <t>major_realm_multipliers:dujie</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1180,6 +1180,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
